--- a/data/trans_orig/IP3101-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3101-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11982</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>7094</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>16956</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25100</t>
+          <t>24834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15637</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>13072</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26554</t>
+          <t>25898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12647</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23865</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21873</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25966</t>
+          <t>26116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41565</t>
+          <t>42618</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19001</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>17268</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>18127</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32100</t>
+          <t>31932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32226</t>
+          <t>32483</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47201</t>
+          <t>47113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26767</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40891</t>
+          <t>41450</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63539</t>
+          <t>63322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84913</t>
+          <t>84254</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19082</t>
+          <t>18641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35696</t>
+          <t>34220</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>18449</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34716</t>
+          <t>34445</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41739</t>
+          <t>41841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64252</t>
+          <t>63937</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44112</t>
+          <t>43916</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35904</t>
+          <t>36434</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56306</t>
+          <t>56670</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67707</t>
+          <t>66274</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95187</t>
+          <t>95543</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57407</t>
+          <t>57160</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82442</t>
+          <t>80949</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>73200</t>
+          <t>72261</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>99418</t>
+          <t>100374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>138314</t>
+          <t>136885</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>174224</t>
+          <t>172857</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68588</t>
+          <t>68049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94870</t>
+          <t>94663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86303</t>
+          <t>87389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114585</t>
+          <t>114988</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,47 +1803,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>19,44%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>25,58%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>181514</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>161251</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>202431</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>21,62%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>19,2%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>25,49%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>181514</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>162354</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>203203</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>21,62%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>19,34%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164753</t>
+          <t>163991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>195606</t>
+          <t>195271</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>176216</t>
+          <t>174280</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208694</t>
+          <t>208675</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>349088</t>
+          <t>347131</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>396970</t>
+          <t>395496</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20381</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14334</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21796</t>
+          <t>22316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23957</t>
+          <t>24474</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40661</t>
+          <t>41676</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14648</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28965</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43281</t>
+          <t>42555</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64453</t>
+          <t>64966</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,49%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24508</t>
+          <t>25396</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42279</t>
+          <t>41344</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28079</t>
+          <t>27605</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44421</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56885</t>
+          <t>57752</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80834</t>
+          <t>81061</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70507</t>
+          <t>70300</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91606</t>
+          <t>91455</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61887</t>
+          <t>60945</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81662</t>
+          <t>79864</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>136600</t>
+          <t>137243</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>164999</t>
+          <t>166255</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>55,0%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31214</t>
+          <t>32150</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51264</t>
+          <t>52636</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33935</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53821</t>
+          <t>53181</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69344</t>
+          <t>69815</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97738</t>
+          <t>97999</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39701</t>
+          <t>40964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62275</t>
+          <t>62382</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>52544</t>
+          <t>52924</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76392</t>
+          <t>76874</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>98579</t>
+          <t>99068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>132672</t>
+          <t>131934</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>104322</t>
+          <t>102864</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>136645</t>
+          <t>136221</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>106932</t>
+          <t>106269</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>138387</t>
+          <t>139630</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>218555</t>
+          <t>218526</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>263775</t>
+          <t>265843</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>111057</t>
+          <t>111690</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143816</t>
+          <t>144523</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130411</t>
+          <t>129726</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>165261</t>
+          <t>165925</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>250632</t>
+          <t>252249</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>297914</t>
+          <t>301849</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>279828</t>
+          <t>281288</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>320461</t>
+          <t>320540</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>277738</t>
+          <t>277395</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>317027</t>
+          <t>319461</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>567129</t>
+          <t>569161</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>624764</t>
+          <t>627237</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10429</t>
+          <t>10804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>13629</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>16895</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10574</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22888</t>
+          <t>22652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>14740</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28023</t>
+          <t>28485</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29865</t>
+          <t>28692</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47877</t>
+          <t>47722</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17011</t>
+          <t>16850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>13026</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>26011</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46553</t>
+          <t>46283</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61083</t>
+          <t>61824</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28479</t>
+          <t>29282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43651</t>
+          <t>44014</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79153</t>
+          <t>80674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101802</t>
+          <t>102206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,62%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12315</t>
+          <t>12312</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26360</t>
+          <t>26529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23625</t>
+          <t>23314</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41431</t>
+          <t>42226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>21934</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38660</t>
+          <t>39659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23860</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40844</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49121</t>
+          <t>49466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74747</t>
+          <t>75159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58474</t>
+          <t>58213</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>83233</t>
+          <t>83247</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62730</t>
+          <t>62511</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87507</t>
+          <t>87229</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>126089</t>
+          <t>126726</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>163524</t>
+          <t>161370</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64699</t>
+          <t>63593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89615</t>
+          <t>90778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62246</t>
+          <t>62132</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87395</t>
+          <t>86930</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133640</t>
+          <t>133591</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>171204</t>
+          <t>170497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>207975</t>
+          <t>208124</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>241930</t>
+          <t>241805</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>238234</t>
+          <t>239395</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>272485</t>
+          <t>272187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>455674</t>
+          <t>454531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>502785</t>
+          <t>500604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,81%</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25460</t>
+          <t>25026</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>28171</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28573</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46807</t>
+          <t>48210</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>29888</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34795</t>
+          <t>35609</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39136</t>
+          <t>39057</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59396</t>
+          <t>60031</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95959</t>
+          <t>96520</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115047</t>
+          <t>115024</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86842</t>
+          <t>85816</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105903</t>
+          <t>106140</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>188666</t>
+          <t>187841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216976</t>
+          <t>215631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23396</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>18397</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33917</t>
+          <t>35085</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32190</t>
+          <t>32069</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52490</t>
+          <t>52663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34426</t>
+          <t>35886</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56918</t>
+          <t>56635</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39538</t>
+          <t>39731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>61662</t>
+          <t>61369</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>81445</t>
+          <t>80314</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>111476</t>
+          <t>110998</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>89343</t>
+          <t>90944</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>120184</t>
+          <t>121122</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>99399</t>
+          <t>99252</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>132242</t>
+          <t>131284</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>198525</t>
+          <t>198467</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>242605</t>
+          <t>242932</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>91921</t>
+          <t>91566</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>121819</t>
+          <t>124240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97841</t>
+          <t>95960</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>128700</t>
+          <t>128263</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>195449</t>
+          <t>195654</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>239138</t>
+          <t>241204</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>361613</t>
+          <t>361213</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>404971</t>
+          <t>404376</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>366290</t>
+          <t>366453</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>408953</t>
+          <t>409602</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>744686</t>
+          <t>742420</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>801735</t>
+          <t>801405</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,56%</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>641</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2676</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>10195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5442</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14948</t>
+          <t>14614</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10776</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>21816</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11930</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24485</t>
+          <t>24884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29048</t>
+          <t>29039</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41091</t>
+          <t>40844</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37257</t>
+          <t>37210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50451</t>
+          <t>49876</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69261</t>
+          <t>70244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87075</t>
+          <t>87802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24004</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18699</t>
+          <t>18572</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36118</t>
+          <t>34738</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>20640</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23798</t>
+          <t>23934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41247</t>
+          <t>41274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49326</t>
+          <t>49379</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74278</t>
+          <t>74152</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>55806</t>
+          <t>55531</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81924</t>
+          <t>80103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59294</t>
+          <t>59634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85547</t>
+          <t>85565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>123510</t>
+          <t>120927</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>158577</t>
+          <t>155924</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93108</t>
+          <t>93505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123146</t>
+          <t>123439</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95467</t>
+          <t>97160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125983</t>
+          <t>127490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198921</t>
+          <t>199818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242495</t>
+          <t>242209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211365</t>
+          <t>209951</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245419</t>
+          <t>243632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>211479</t>
+          <t>208550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>247057</t>
+          <t>245866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>432844</t>
+          <t>432014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>481875</t>
+          <t>481744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,46%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>11793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22350</t>
+          <t>21761</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19793</t>
+          <t>18662</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34707</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15874</t>
+          <t>16219</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30884</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38248</t>
+          <t>38195</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60090</t>
+          <t>58930</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23725</t>
+          <t>23995</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40080</t>
+          <t>40204</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>23737</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40938</t>
+          <t>40502</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51465</t>
+          <t>52302</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75404</t>
+          <t>76131</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82268</t>
+          <t>81310</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102073</t>
+          <t>101931</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90715</t>
+          <t>91164</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111938</t>
+          <t>111573</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>179519</t>
+          <t>178687</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208869</t>
+          <t>208085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,72%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18304</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17818</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35293</t>
+          <t>34696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27705</t>
+          <t>28435</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>47792</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29067</t>
+          <t>29039</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49439</t>
+          <t>47999</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33056</t>
+          <t>33591</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53558</t>
+          <t>54521</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67442</t>
+          <t>67899</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94802</t>
+          <t>95817</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>87713</t>
+          <t>89453</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>118517</t>
+          <t>119488</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>84801</t>
+          <t>84749</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>116741</t>
+          <t>115536</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>182903</t>
+          <t>182671</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>228309</t>
+          <t>225981</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>131878</t>
+          <t>130459</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>165613</t>
+          <t>165816</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>134215</t>
+          <t>136184</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>169797</t>
+          <t>173362</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>273208</t>
+          <t>277444</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>324835</t>
+          <t>323854</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -9148,47 +9148,47 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>332376</t>
+          <t>333778</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
+          <t>374509</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>54,1%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>50,97%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>57,19%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>375301</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>54,1%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>50,76%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>57,31%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>375301</t>
-        </is>
-      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>353823</t>
+          <t>353209</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>398210</t>
+          <t>396658</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>698054</t>
+          <t>697862</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>760756</t>
+          <t>761185</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
